--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -711,25 +711,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H8">
-        <v>28.57</v>
+        <v>11.43</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -830,22 +830,25 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>18.92</v>
+      </c>
+      <c r="I2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -958,22 +961,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.11</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>13.89</v>
+      </c>
+      <c r="I6">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -990,22 +996,25 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I7">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1022,22 +1031,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>62.86</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>37.14</v>
+      </c>
+      <c r="I8">
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1135,19 +1147,19 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H2">
-        <v>32.43</v>
+        <v>18.92</v>
       </c>
       <c r="I2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1287,7 +1299,7 @@
         <v>13.89</v>
       </c>
       <c r="I6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1310,19 +1322,19 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>82.86</v>
+        <v>77.14</v>
       </c>
       <c r="H7">
-        <v>17.14</v>
+        <v>22.86</v>
       </c>
       <c r="I7">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1345,25 +1357,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H8">
-        <v>28.57</v>
+        <v>11.43</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,6 +94,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -146,8 +150,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -448,42 +454,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -506,19 +515,19 @@
       <c r="F2">
         <v>12</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>67.56999999999999</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>32.43</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -541,19 +550,19 @@
       <c r="F3">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>69.44</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>30.56</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
         <v>11</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>30.56</v>
       </c>
     </row>
@@ -576,19 +585,19 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>91.3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>8.699999999999999</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -611,19 +620,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>86.95999999999999</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>13.04</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>4.35</v>
       </c>
     </row>
@@ -646,19 +655,19 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>86.11</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>13.89</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -681,19 +690,19 @@
       <c r="F7">
         <v>6</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>82.86</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>17.14</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -716,19 +725,19 @@
       <c r="F8">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>11.43</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>10</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>11.43</v>
       </c>
     </row>
@@ -751,19 +760,19 @@
       <c r="F9">
         <v>14</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>62.16</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>37.84</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>10.81</v>
       </c>
     </row>
@@ -777,42 +786,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -835,19 +847,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>81.08</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>18.92</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -870,16 +882,16 @@
       <c r="F3">
         <v>36</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <v>100</v>
       </c>
       <c r="J3">
         <v>36</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>100</v>
       </c>
     </row>
@@ -902,16 +914,16 @@
       <c r="F4">
         <v>23</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="J4">
         <v>23</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>100</v>
       </c>
     </row>
@@ -934,16 +946,16 @@
       <c r="F5">
         <v>23</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>100</v>
       </c>
       <c r="J5">
         <v>23</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
     </row>
@@ -966,19 +978,19 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>86.11</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>13.89</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1001,19 +1013,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>77.14</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>22.86</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1036,19 +1048,19 @@
       <c r="F8">
         <v>13</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>62.86</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>37.14</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J8">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>37.14</v>
       </c>
     </row>
@@ -1071,16 +1083,16 @@
       <c r="F9">
         <v>37</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>100</v>
       </c>
       <c r="J9">
         <v>37</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1094,42 +1106,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1152,19 +1167,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>81.08</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>18.92</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1187,19 +1202,19 @@
       <c r="F3">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>69.44</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>30.56</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
         <v>11</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>30.56</v>
       </c>
     </row>
@@ -1222,19 +1237,19 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>91.3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>8.699999999999999</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1257,19 +1272,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>86.95999999999999</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>13.04</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>4.35</v>
       </c>
     </row>
@@ -1292,19 +1307,19 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>86.11</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>13.89</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1327,19 +1342,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>77.14</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>22.86</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1362,19 +1377,19 @@
       <c r="F8">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>11.43</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>9.9</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>11.43</v>
       </c>
     </row>
@@ -1397,19 +1412,19 @@
       <c r="F9">
         <v>14</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>62.16</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>37.84</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>10.81</v>
       </c>
     </row>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -95,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -545,25 +545,25 @@
         <v>36</v>
       </c>
       <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="H3" s="1">
+        <v>27.78</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1">
         <v>25</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="H3" s="1">
-        <v>30.56</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -767,13 +767,13 @@
         <v>37.84</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -877,22 +877,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>36.11</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -909,22 +912,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>82.61</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>17.39</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -941,22 +947,25 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>13.04</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1043,25 +1052,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>62.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>37.14</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>37.14</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1078,22 +1087,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>56.76</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>43.24</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1197,25 +1209,25 @@
         <v>36</v>
       </c>
       <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="H3" s="1">
+        <v>27.78</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1">
         <v>25</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="H3" s="1">
-        <v>30.56</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1279,7 +1291,7 @@
         <v>13.04</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1384,7 +1396,7 @@
         <v>11.43</v>
       </c>
       <c r="I8" s="2">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1407,25 +1419,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>62.16</v>
+        <v>56.76</v>
       </c>
       <c r="H9" s="1">
-        <v>37.84</v>
+        <v>43.24</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -545,25 +545,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="H3" s="1">
-        <v>27.78</v>
+        <v>22.22</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -627,13 +627,13 @@
         <v>13.04</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -720,25 +720,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
       <c r="I8" s="2">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -877,25 +877,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>63.89</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>36.11</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -912,25 +912,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>82.61</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>17.39</v>
+        <v>13.04</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>13.04</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -947,25 +947,25 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H5" s="1">
-        <v>13.04</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1052,25 +1052,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1">
-        <v>28.57</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>28.57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1209,25 +1209,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>27.78</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1279,25 +1279,25 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H5" s="1">
-        <v>13.04</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1384,25 +1384,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
       <c r="I8" s="2">
         <v>9.800000000000001</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -720,25 +720,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -912,25 +912,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H4" s="1">
-        <v>13.04</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -959,13 +959,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1052,25 +1052,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1174,16 +1174,16 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>81.08</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>18.92</v>
+        <v>13.51</v>
       </c>
       <c r="I2" s="2">
         <v>8.1</v>
@@ -1209,19 +1209,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H3" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1244,19 +1244,19 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1279,19 +1279,19 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1314,19 +1314,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>86.11</v>
+        <v>94.44</v>
       </c>
       <c r="H6" s="1">
-        <v>13.89</v>
+        <v>5.56</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1349,19 +1349,19 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>22.86</v>
+        <v>5.71</v>
       </c>
       <c r="I7" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1384,25 +1384,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1419,19 +1419,19 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>56.76</v>
+        <v>72.97</v>
       </c>
       <c r="H9" s="1">
-        <v>43.24</v>
+        <v>27.03</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20211.xlsx
@@ -1209,19 +1209,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H3" s="1">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
